--- a/UniqueRankList/Etkinlik_Takvimi.xlsx
+++ b/UniqueRankList/Etkinlik_Takvimi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\burak\OneDrive\Masaüstü\UniqueRankList\UniqueRankList\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE90F38-A988-4362-ADAA-83A71B9CB217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B36EFE-69AE-4EDC-BEB1-B0F5ED8AAA10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2C64AA72-15CA-4D74-91F3-A838DF0FB5EE}"/>
   </bookViews>
@@ -995,319 +995,319 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>2.0833333333333332E-2</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>4.1666666666666664E-2</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>0.10416666666666667</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>0.125</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>0.16666666666666666</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>0.20833333333333334</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>0.29166666666666669</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>0.29166666666666669</v>
+        <v>0.95833333333333337</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>0.35416666666666669</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>0.375</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>0.41666666666666669</v>
+        <v>0.10416666666666667</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>0.45833333333333331</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>0.47916666666666669</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>11</v>
@@ -1333,59 +1333,59 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>0.54166666666666663</v>
+        <v>0.97916666666666663</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>0.58333333333333337</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>0.625</v>
+        <v>0.125</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>10</v>
@@ -1411,33 +1411,33 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>0.70833333333333337</v>
+        <v>0.20833333333333334</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>10</v>
@@ -1463,85 +1463,85 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>0.83333333333333337</v>
+        <v>0.375</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <v>0.85416666666666663</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>0.875</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <v>0.875</v>
+        <v>0.625</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>10</v>
@@ -1567,54 +1567,54 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <v>0.89583333333333337</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <v>0.91666666666666663</v>
+        <v>0.875</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1622,77 +1622,77 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
-        <v>0.95833333333333337</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
-        <v>0.97916666666666663</v>
+        <v>0.875</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
